--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1470-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1470-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E688289-FE94-4954-9AD8-1E1FD1905CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E57695A-EFA2-4025-A55A-09CA886B6E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{1EA4A629-A26E-4A7B-A52F-B5D8B6842501}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{0AAFEC81-3574-4E50-8E0D-1770AB46E184}"/>
   </bookViews>
   <sheets>
     <sheet name="1470-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1496,27 +1496,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9668589B-A7C6-4138-9D14-3E1A93027A3F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43223432-012E-4D9F-9681-3BE928180E10}">
   <dimension ref="A1:X48"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1550,7 +1550,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1586,7 +1586,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1706,7 +1706,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2024</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2023</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2022</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2021</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2020</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2019</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2018</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>2017</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2016</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2015</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2014</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2013</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2012</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2011</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2010</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2009</v>
       </c>
@@ -3522,7 +3522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2008</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>2007</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2006</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>2005</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>2004</v>
       </c>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>2003</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2002</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>2001</v>
       </c>
@@ -4098,7 +4098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>2000</v>
       </c>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>1999</v>
       </c>
@@ -4242,7 +4242,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>1998</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="35">
         <v>1997</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>1996</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="35">
         <v>1994</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>1993</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="35">
         <v>1992</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>1991</v>
       </c>
@@ -4746,7 +4746,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="35">
         <v>1990</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="37" t="s">
         <v>53</v>
       </c>
